--- a/PPT's/Observation table.xlsx
+++ b/PPT's/Observation table.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Anu\Projects\Traffic Management\PPT's\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6EBCCD20-F857-4016-8FC7-A2E5EF6333ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A63A3FD5-EE3C-46AA-BB83-93E22B48D605}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="13695" xr2:uid="{C1376DF6-C32B-46B1-85CA-C57768C49BE5}"/>
   </bookViews>
